--- a/Data/ConditionMenu.xlsx
+++ b/Data/ConditionMenu.xlsx
@@ -1,34 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84827589-6D19-4DC7-B0FC-88DCFA53BFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="3840" yWindow="615" windowWidth="23790" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="ConditionGroup" sheetId="2" r:id="rId1"/>
-    <sheet name="ConditionRow" sheetId="3" r:id="rId2"/>
+    <sheet state="visible" name="Info" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="ConditionGroup" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="ConditionRow" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+  <si>
+    <t>ConditionMenu：能力「能不能發動」的判斷集合</t>
+  </si>
+  <si>
+    <t>分兩層：</t>
+  </si>
+  <si>
+    <t>ConditionGroup：條件群組的邏輯</t>
+  </si>
   <si>
     <t>ConditionGroupId</t>
   </si>
   <si>
+    <t>Logic（AND / OR）</t>
+  </si>
+  <si>
+    <t>代表這一組條件要怎麼合併判斷。</t>
+  </si>
+  <si>
+    <t>ConditionRow：一條條可計算的條件</t>
+  </si>
+  <si>
     <t>ConditionType</t>
   </si>
   <si>
+    <t>（可選參數欄位：Value1/Value2 或 ParamKey/ParamValue）</t>
+  </si>
+  <si>
+    <t>ConditionRow 不做行為，只回傳 True/False（以及失敗原因給 log）。</t>
+  </si>
+  <si>
     <t>Logic</t>
   </si>
   <si>
@@ -38,76 +54,90 @@
     <t>AND</t>
   </si>
   <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>Param4</t>
+  </si>
+  <si>
     <t>OwnerClassEqualsPartnerClass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -297,74 +327,147 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="15.5703125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="8">
+      <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="10">
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="14">
+      <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="16">
+      <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="18">
+      <c r="C18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="15.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.0"/>
+    <col customWidth="1" min="2" max="2" width="24.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/ConditionMenu.xlsx
+++ b/Data/ConditionMenu.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9C1F53-AD83-4A78-85D7-8134E5B505AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Info" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="ConditionGroup" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="ConditionRow" sheetId="3" r:id="rId6"/>
+    <sheet name="Info" sheetId="1" r:id="rId1"/>
+    <sheet name="ConditionGroup" sheetId="2" r:id="rId2"/>
+    <sheet name="ConditionRow" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -72,17 +81,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -91,7 +109,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -101,43 +119,40 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -327,87 +342,92 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="C8:C28"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="8">
+    <row r="8" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="15.63"/>
+    <col min="1" max="2" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -415,7 +435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -424,22 +444,24 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.0"/>
-    <col customWidth="1" min="2" max="2" width="24.75"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -459,7 +481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -468,6 +490,7 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>